--- a/SGC-CKN/Excel/36844c7f-74fc-4751-b1ef-fb00e1087186_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P325_D1200_13-04-2026.xlsx
+++ b/SGC-CKN/Excel/36844c7f-74fc-4751-b1ef-fb00e1087186_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P325_D1200_13-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="78">
   <si>
     <t>Dự án</t>
   </si>
@@ -103,7 +103,7 @@
 13/04/2026</t>
   </si>
   <si>
-    <t>Chiều dài tính toán (6.9 - 4.88)</t>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -114,9 +114,6 @@
   <si>
     <t xml:space="preserve">10:20
 13/04/2026</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>3</t>
@@ -1309,24 +1306,24 @@
         <v>2.4</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="13">
         <v>-7.7</v>
@@ -1344,24 +1341,24 @@
         <v>20.25</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-21.2</v>
@@ -1379,24 +1376,24 @@
         <v>11.44</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-27.3</v>
@@ -1414,24 +1411,24 @@
         <v>1.78</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>44</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>45</v>
       </c>
       <c r="F16" s="22">
         <v>-31.1</v>
@@ -1449,24 +1446,24 @@
         <v>9</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-34.1</v>
@@ -1484,24 +1481,24 @@
         <v>9.6</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>50</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>51</v>
       </c>
       <c r="F18" s="28">
         <v>-37.3</v>
@@ -1519,24 +1516,24 @@
         <v>13.8</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
+      <c r="D19" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>54</v>
       </c>
       <c r="F19" s="31">
         <v>-44.2</v>
@@ -1554,24 +1551,24 @@
         <v>10.97</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="D20" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="36" t="s">
         <v>56</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>57</v>
       </c>
       <c r="F20" s="34">
         <v>-57</v>
@@ -1589,24 +1586,24 @@
         <v>8.4</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>59</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>60</v>
       </c>
       <c r="F21" s="16">
         <v>-61.2</v>
@@ -1624,24 +1621,24 @@
         <v>4.95</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="38" t="s">
+      <c r="D22" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="39" t="s">
         <v>62</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>63</v>
       </c>
       <c r="F22" s="37">
         <v>-64.5</v>
@@ -1659,24 +1656,24 @@
         <v>2.8</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="F23" s="5">
         <v>-65.9</v>
@@ -1694,24 +1691,24 @@
         <v>9.6</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="D24" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>68</v>
       </c>
       <c r="F24" s="9">
         <v>-73.1</v>
@@ -1729,12 +1726,12 @@
         <v>2.31</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
@@ -1840,31 +1837,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1933,7 +1930,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1962,7 +1959,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1991,7 +1988,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -2020,7 +2017,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -2049,7 +2046,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -2078,7 +2075,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -2107,7 +2104,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -2136,7 +2133,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -2165,7 +2162,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="16">
         <v>1</v>
@@ -2194,7 +2191,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="37">
         <v>1</v>
@@ -2223,7 +2220,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -2252,7 +2249,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" s="9">
         <v>1</v>
@@ -2275,13 +2272,13 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B16" s="42" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D16" s="42">
         <v>14</v>
